--- a/event_registration_forms/026_local_business_outreach_request_form--event_registration_forms.xlsx
+++ b/event_registration_forms/026_local_business_outreach_request_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_9.1,_'name':_'event_type',_'label':_'event_type',_'value':_'trade_show'}</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 9.1, 'name': 'event_type', 'label': 'Event Type', 'value': 'Trade Show'}</t>
+          <t>Event Type</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_9.2,_'name':_'event_type',_'label':_'trade_show',_'value':_'trade_show'}</t>
+          <t>trade_show</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 9.2, 'name': 'event_type', 'label': 'Trade Show', 'value': 'Trade Show'}</t>
+          <t>Trade Show</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_9.3,_'name':_'event_type',_'label':_'seminar',_'value':_'seminar'}</t>
+          <t>seminar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 9.3, 'name': 'event_type', 'label': 'Seminar', 'value': 'Seminar'}</t>
+          <t>Seminar</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_10.1,_'name':_'business_services',_'label':_'networking',_'value':_'networking'}</t>
+          <t>networking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 10.1, 'name': 'business_services', 'label': 'Networking', 'value': 'Networking'}</t>
+          <t>Networking</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_10.2,_'name':_'business_services',_'label':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 10.2, 'name': 'business_services', 'label': 'Marketing', 'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_10.3,_'name':_'business_services',_'label':_'sponsorship',_'value':_'sponsorship'}</t>
+          <t>sponsorship</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 10.3, 'name': 'business_services', 'label': 'Sponsorship', 'value': 'Sponsorship'}</t>
+          <t>Sponsorship</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'name':_'collaboration_goals',_'label':_'collaboration',_'value':_'collaboration'}</t>
+          <t>collaboration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'name': 'collaboration_goals', 'label': 'Collaboration', 'value': 'Collaboration'}</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_11.2,_'name':_'collaboration_goals',_'label':_'sponsorship',_'value':_'sponsorship'}</t>
+          <t>sponsorship</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 11.2, 'name': 'collaboration_goals', 'label': 'Sponsorship', 'value': 'Sponsorship'}</t>
+          <t>Sponsorship</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_11.3,_'name':_'collaboration_goals',_'label':_'partnership',_'value':_'partnership'}</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 11.3, 'name': 'collaboration_goals', 'label': 'Partnership', 'value': 'Partnership'}</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'name':_'email',_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'name': 'email', 'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_16.2,_'name':_'phone',_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 16.2, 'name': 'phone', 'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_19.1,_'name':_'location',_'label':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 19.1, 'name': 'location', 'label': 'Online', 'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_19.2,_'name':_'location',_'label':_'local',_'value':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 19.2, 'name': 'location', 'label': 'Local', 'value': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_20.1,_'name':_'event_duration',_'label':_'half-day',_'value':_'half-day'}</t>
+          <t>half-day</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 20.1, 'name': 'event_duration', 'label': 'Half-day', 'value': 'Half-day'}</t>
+          <t>Half-day</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_20.2,_'name':_'event_duration',_'label':_'full-day',_'value':_'full-day'}</t>
+          <t>full-day</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 20.2, 'name': 'event_duration', 'label': 'Full-day', 'value': 'Full-day'}</t>
+          <t>Full-day</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_20.3,_'name':_'event_duration',_'label':_'all-day',_'value':_'all-day'}</t>
+          <t>all-day</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 20.3, 'name': 'event_duration', 'label': 'All-day', 'value': 'All-day'}</t>
+          <t>All-day</t>
         </is>
       </c>
     </row>
